--- a/COORDENADOR.xlsx
+++ b/COORDENADOR.xlsx
@@ -6003,7 +6003,7 @@
         <v>1.2499</v>
       </c>
       <c r="D74" s="22">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="E74" s="22">
         <v>2E-3</v>
